--- a/inst/Parameters_PREFU26.xlsx
+++ b/inst/Parameters_PREFU26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cass-my.sharepoint.com/personal/fergus_cleveland_treasury_govt_nz/Documents/Projects/EFU Updates/PREFU26_Update/PREFU26/outputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cass-my.sharepoint.com/personal/fergus_cleveland_treasury_govt_nz/Documents/Projects/2026/policy_engine/IncomeExplorer/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_B89231273C99636D4E9CACD53C1DF656DDA563ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBF88451-EC2F-4153-A0A2-75118FA844A6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_B89231273C99636D4E9CACD53C1DF656DDA563ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07E0D47-A3B3-4B34-9827-76F5A6AA86D4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
